--- a/experiment3/data_processing/exp_data/10_questions_data_added.xlsx
+++ b/experiment3/data_processing/exp_data/10_questions_data_added.xlsx
@@ -1126,7 +1126,7 @@
         <v>683.6190476190476</v>
       </c>
       <c r="E11" t="n">
-        <v>770.2692307692307</v>
+        <v>768.5833333333334</v>
       </c>
       <c r="F11" t="n">
         <v>663.4090909090909</v>
@@ -1264,7 +1264,7 @@
         <v>541.9285714285714</v>
       </c>
       <c r="G13" t="n">
-        <v>448.5625</v>
+        <v>449.0333333333334</v>
       </c>
       <c r="H13" t="n">
         <v>2.75</v>
@@ -1396,7 +1396,7 @@
         <v>454.0384615384615</v>
       </c>
       <c r="G15" t="n">
-        <v>413.4285714285714</v>
+        <v>405.4444444444445</v>
       </c>
       <c r="H15" t="n">
         <v>2.5625</v>
@@ -2056,7 +2056,7 @@
         <v>657.2083333333334</v>
       </c>
       <c r="G25" t="n">
-        <v>690.64</v>
+        <v>643.5909090909091</v>
       </c>
       <c r="H25" t="n">
         <v>6.4375</v>
